--- a/Assets/_TankRes/excel/tank.xlsx
+++ b/Assets/_TankRes/excel/tank.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="23040" windowHeight="9180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="player" sheetId="1" r:id="rId1"/>
@@ -144,85 +144,85 @@
     <t>0.2,0.1,0.1</t>
   </si>
   <si>
+    <t>2,3</t>
+  </si>
+  <si>
+    <t>tankWhite_0</t>
+  </si>
+  <si>
+    <t>白快坦克</t>
+  </si>
+  <si>
+    <t>0.5,2</t>
+  </si>
+  <si>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>tankWhite_2</t>
+  </si>
+  <si>
+    <t>白满级坦克</t>
+  </si>
+  <si>
+    <t>0.2,0.2,0.1</t>
+  </si>
+  <si>
+    <t>tankWhite_3</t>
+  </si>
+  <si>
+    <t>黄满级坦克</t>
+  </si>
+  <si>
+    <t>0.2,0.2,0.2</t>
+  </si>
+  <si>
+    <t>1,4</t>
+  </si>
+  <si>
+    <t>tankYellow_3</t>
+  </si>
+  <si>
+    <t>绿满级坦克</t>
+  </si>
+  <si>
+    <t>2,2</t>
+  </si>
+  <si>
+    <t>1.5,2</t>
+  </si>
+  <si>
+    <t>tankGreen_3</t>
+  </si>
+  <si>
+    <t>红慢坦克</t>
+  </si>
+  <si>
+    <t>2,2.5</t>
+  </si>
+  <si>
+    <t>0.2,0.2,0.3</t>
+  </si>
+  <si>
+    <t>tankRad_0</t>
+  </si>
+  <si>
+    <t>红快坦克</t>
+  </si>
+  <si>
+    <t>0.5,0.8</t>
+  </si>
+  <si>
+    <t>0.3,0.1,0.3</t>
+  </si>
+  <si>
+    <t>tankRad_2</t>
+  </si>
+  <si>
+    <t>红满级坦克</t>
+  </si>
+  <si>
     <t>1,3</t>
-  </si>
-  <si>
-    <t>tankWhite_0</t>
-  </si>
-  <si>
-    <t>白快坦克</t>
-  </si>
-  <si>
-    <t>0.5,2</t>
-  </si>
-  <si>
-    <t>1,2</t>
-  </si>
-  <si>
-    <t>tankWhite_2</t>
-  </si>
-  <si>
-    <t>白满级坦克</t>
-  </si>
-  <si>
-    <t>0.2,0.2,0.1</t>
-  </si>
-  <si>
-    <t>tankWhite_3</t>
-  </si>
-  <si>
-    <t>黄满级坦克</t>
-  </si>
-  <si>
-    <t>2,3</t>
-  </si>
-  <si>
-    <t>0.2,0.2,0.2</t>
-  </si>
-  <si>
-    <t>1,4</t>
-  </si>
-  <si>
-    <t>tankYellow_3</t>
-  </si>
-  <si>
-    <t>绿满级坦克</t>
-  </si>
-  <si>
-    <t>2,2</t>
-  </si>
-  <si>
-    <t>1.5,2</t>
-  </si>
-  <si>
-    <t>tankGreen_3</t>
-  </si>
-  <si>
-    <t>红慢坦克</t>
-  </si>
-  <si>
-    <t>2,2.5</t>
-  </si>
-  <si>
-    <t>0.2,0.2,0.3</t>
-  </si>
-  <si>
-    <t>tankRad_0</t>
-  </si>
-  <si>
-    <t>红快坦克</t>
-  </si>
-  <si>
-    <t>0.5,0.8</t>
-  </si>
-  <si>
-    <t>0.3,0.1,0.3</t>
-  </si>
-  <si>
-    <t>tankRad_2</t>
-  </si>
-  <si>
-    <t>红满级坦克</t>
   </si>
   <si>
     <t>0.3,0.2,0.3</t>
@@ -1662,16 +1662,16 @@
         <v>203</v>
       </c>
       <c r="H8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="L8" s="2" t="b">
         <v>0</v>
@@ -1682,7 +1682,7 @@
         <v>205</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" s="2">
         <v>4</v>
@@ -1700,16 +1700,16 @@
         <v>204</v>
       </c>
       <c r="H9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="J9" s="2" t="s">
+      <c r="K9" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="L9" s="2" t="b">
         <v>0</v>
@@ -1720,7 +1720,7 @@
         <v>301</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C10" s="2">
         <v>1</v>
@@ -1738,16 +1738,16 @@
         <v>201</v>
       </c>
       <c r="H10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="J10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K10" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="L10" s="2" t="b">
         <v>1</v>
@@ -1758,7 +1758,7 @@
         <v>302</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C11" s="2">
         <v>2</v>
@@ -1776,16 +1776,16 @@
         <v>202</v>
       </c>
       <c r="H11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="J11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K11" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="L11" s="2" t="b">
         <v>1</v>
@@ -1796,7 +1796,7 @@
         <v>303</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C12" s="2">
         <v>1</v>
@@ -1814,7 +1814,7 @@
         <v>205</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>65</v>
